--- a/outs.xlsx
+++ b/outs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DOCS\LINGUAGENS\sites html e css\Fast_check-out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14DAB64-0E7F-4073-B630-9E51F7CEBA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2261285-75FA-462A-AFC8-19B6C67DB056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,10 +54,10 @@
     <t>Não</t>
   </si>
   <si>
-    <t>Luiz Carlos ; Marcia Loba</t>
-  </si>
-  <si>
-    <t>Mauro Coelho Silva ; Marcia Loba</t>
+    <t>Lucas silva</t>
+  </si>
+  <si>
+    <t>Lucas lima</t>
   </si>
 </sst>
 </file>
@@ -403,7 +403,7 @@
         <v>52253</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>507</v>
@@ -423,7 +423,7 @@
         <v>52254</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>1209</v>
